--- a/Thống kê Model.xlsx
+++ b/Thống kê Model.xlsx
@@ -5,22 +5,22 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PP NCKH\fx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ReiJunn\Documents\GitHub\Code-NCKH\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9E47DE8-136D-4D87-B0F0-0FA51DA6F9D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CF9123D-6DCD-40FC-BFC6-48448C2E2BAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Bây giờ hãy sửa lại file Thống " sheetId="1" r:id="rId1"/>
+    <sheet name="kết quả dự báo mới đã tốt hơn, " sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
   <si>
     <t>Phân khúc</t>
   </si>
@@ -40,7 +40,7 @@
     <t>Đặc trưng tóm tắt chuỗi dữ liệu (Heuristics)</t>
   </si>
   <si>
-    <t>Quyết định Lưu kho &amp; Điều phối thực tế (Đã tích hợp Trọng số Tết)</t>
+    <t>Quyết định Lưu kho &amp; Điều phối thực tế (Đã tích hợp Hậu xử lý)</t>
   </si>
   <si>
     <t>Phân khúc A(ML Candidate)Tổng: 96 mã</t>
@@ -49,61 +49,37 @@
     <t>ARIMA</t>
   </si>
   <si>
-    <t>40.6%</t>
-  </si>
-  <si>
-    <t>14.3%</t>
-  </si>
-  <si>
     <t>Chuỗi liên tục, tự tương quan tuyến tính vững chắc, không gãy cấu trúc.</t>
   </si>
   <si>
-    <t>Dự báo nền rất vững. Nhân chuỗi hệ số lịch sử theo tiến trình [0.85 → 0.45 → 1.30]. Hạ mạnh lượng nhập tháng 2 tránh nghẽn dòng tiền, đẩy max công suất tháng 3.</t>
+    <t>Dự báo nền vững chắc. Áp dụng hệ số lịch sử [0.85 → 0.45 → 1.30]. Hạ mạnh lượng nhập tháng 2 nhưng luôn giữ trên Ngưỡng đệm 10% để chống đứt gãy cung ứng cục bộ.</t>
   </si>
   <si>
     <t>Ensemble</t>
   </si>
   <si>
-    <t>24.0%</t>
-  </si>
-  <si>
-    <t>8.5%</t>
-  </si>
-  <si>
-    <t>Biến động đa chiều, các thuật toán đơn lẻ có xu hướng Overfitting (học vẹt) nay đã được bù trừ sai số nhờ trung bình cộng.</t>
-  </si>
-  <si>
-    <t>Mô hình Ensemble cho kết quả nền mang tính cào bằng mượt mà. Bộ trọng số lịch sử bẻ gãy đường phẳng này, tạo ra điểm đáy cực hạn cho tháng 2 (×0.45).</t>
+    <t>Biến động đa chiều, thuật toán đơn lẻ có xu hướng bù trừ sai số nhờ trung bình cộng.</t>
+  </si>
+  <si>
+    <t>Mô hình Kết hợp cho ra đường dự báo mượt mà. Hệ số Tết bẻ gãy đường phẳng này, kết hợp làm tròn lên (Ceiling) đảm bảo linh hoạt đáp ứng sóng thị trường.</t>
   </si>
   <si>
     <t>LSTM</t>
   </si>
   <si>
-    <t>18.8%</t>
-  </si>
-  <si>
-    <t>6.6%</t>
-  </si>
-  <si>
-    <t>Chuỗi dài, phụ thuộc và ghi nhớ chu kỳ lịch sử sâu (sau khi đã được làm mượt qua 5 vòng lặp).</t>
-  </si>
-  <si>
-    <t>Giữ nguyên dự báo cấu trúc dài hạn, áp trọng số lịch sử để dời lịch trình điều phối hàng: đóng băng xuất kho tháng 2 dồn sang cung ứng cho tháng 3.</t>
+    <t>Chuỗi dài, phụ thuộc và ghi nhớ chu kỳ lịch sử sâu từ nhiều tháng trước.</t>
+  </si>
+  <si>
+    <t>Giữ nguyên dự báo cấu trúc dài hạn, tiến hành dời lịch trình điều phối: ép xuất kho tháng 2 về mức đệm tối thiểu, dồn toàn lực cung ứng cho tháng 3.</t>
   </si>
   <si>
     <t>Prophet</t>
   </si>
   <si>
-    <t>16.7%</t>
-  </si>
-  <si>
-    <t>5.9%</t>
-  </si>
-  <si>
     <t>Xu hướng rõ rệt hoặc đang thoái trào dốc đứng ở cuối chu kỳ sống.</t>
   </si>
   <si>
-    <t>Kết hợp gia tốc giảm xu hướng của Prophet và trọng số thấp điểm tháng 2 (0.45) để đẩy nhanh xả hàng tồn cũ (clear-stock).</t>
+    <t>Kết hợp gia tốc giảm của Prophet. Nếu mã đã "ngủ đông" 6 tháng, thuật toán sẽ chính thức cho kết quả bằng 0 để Khai tử (Clear-stock) triệt để.</t>
   </si>
   <si>
     <t>Phân khúc C(Sparse)Tổng: 176 mã</t>
@@ -112,58 +88,37 @@
     <t>Naive</t>
   </si>
   <si>
-    <t>55.1%</t>
-  </si>
-  <si>
-    <t>35.7%</t>
-  </si>
-  <si>
     <t>Biến động mạnh, ngẫu nhiên, nhiễu lấn át hoàn toàn tín hiệu quá khứ.</t>
   </si>
   <si>
-    <t>Dự báo nền giữ nguyên mức tháng gần nhất. Tháng 2 Tết áp trọng số ngặt nghèo 0.20 để khóa chặt luồng tự động nhập hàng.</t>
+    <t>Dự báo nền giữ nguyên mức tháng gần nhất. Tháng 2 Tết áp trọng số ngặt nghèo (0.20) nhưng được bảo vệ bởi Tồn kho đệm tối thiểu, đảm bảo luôn có ít nhất 1-2 đơn vị dự phòng.</t>
   </si>
   <si>
     <t>MA3</t>
   </si>
   <si>
-    <t>21.6%</t>
-  </si>
-  <si>
-    <t>14.0%</t>
-  </si>
-  <si>
     <t>Thưa thớt nhẹ, ổn định cục bộ theo quý, nhu cầu mang tính giật cục.</t>
   </si>
   <si>
-    <t>Trọng số lịch sử bắt buộc phải can thiệp để kéo tụt sản lượng tháng 2 xuống đáy, tránh hiện tượng tồn kho làm phẳng cơ học của MA3.</t>
+    <t>Trọng số lịch sử đánh gãy hiện tượng tồn kho làm phẳng cơ học của MA3. Khống chế lượng hàng nhập rác, chỉ nhập khi vượt ngưỡng an toàn.</t>
   </si>
   <si>
     <t>Croston</t>
   </si>
   <si>
-    <t>14.2%</t>
-  </si>
-  <si>
-    <t>9.2%</t>
-  </si>
-  <si>
     <t>Đứt quãng nghiêm trọng nhưng khối lượng tương đối đồng đều khi phát sinh.</t>
   </si>
   <si>
-    <t>Croston tối ưu được kích cỡ giỏ hàng. Trọng số lịch sử tháng 2 (0.20) sẽ đánh thẳng vào xác suất xuất hiện đơn hàng, đẩy nó về mức 0.</t>
+    <t>Croston tối ưu được kích cỡ giỏ hàng. Trọng số 0.20 đánh tụt xác suất xuất hiện đơn vào dịp lễ, chặn đứng luồng nhập hàng tự động.</t>
   </si>
   <si>
     <t>MA6</t>
   </si>
   <si>
-    <t>9.1%</t>
-  </si>
-  <si>
     <t>Thưa thớt nặng, nhu cầu đi ngang ổn định trên diện trung hạn (nửa năm).</t>
   </si>
   <si>
-    <t>Nhóm phụ tùng dự phòng. Trọng số lịch sử giữ ở mức an toàn ổn định, không can thiệp quá sâu do ít chịu rủi ro hao mòn.</t>
+    <t>Nhóm phụ tùng dự phòng. Trọng số lịch sử giữ ở mức an toàn. Kích hoạt quy tắc "Làm tròn lên" để kho luôn duy trì trạng thái phòng thủ thụ động.</t>
   </si>
 </sst>
 </file>
@@ -181,6 +136,7 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -204,9 +160,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -226,6 +183,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </font>
     </dxf>
@@ -243,6 +201,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </font>
     </dxf>
@@ -260,6 +219,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </font>
     </dxf>
@@ -277,6 +237,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </font>
     </dxf>
@@ -294,6 +255,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </font>
     </dxf>
@@ -311,6 +273,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </font>
     </dxf>
@@ -328,6 +291,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </font>
     </dxf>
@@ -345,6 +309,7 @@
         <sz val="10"/>
         <color theme="1"/>
         <name val="Arial"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </font>
     </dxf>
@@ -362,18 +327,18 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{CED136EA-9767-45FC-BB0B-BC2B1F29324A}" name="Table1" displayName="Table1" ref="A1:G9" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
-  <autoFilter ref="A1:G9" xr:uid="{CED136EA-9767-45FC-BB0B-BC2B1F29324A}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{A8EA3589-351B-4F3C-ACB1-34FE28B4F156}" name="Table1" displayName="Table1" ref="A1:G9" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+  <autoFilter ref="A1:G9" xr:uid="{A8EA3589-351B-4F3C-ACB1-34FE28B4F156}"/>
   <tableColumns count="7">
-    <tableColumn id="1" xr3:uid="{CCB2C030-3B6B-40B0-8295-2222D0D2B7ED}" name="Phân khúc"/>
-    <tableColumn id="2" xr3:uid="{03CB693E-CCD8-44B1-A2E1-704C2BE1D944}" name="Mô hình Vô địch" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{3AAD4E2F-BE5B-4838-A7DA-A2CC24735353}" name="Số lượng mã" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{A71677A8-02BF-4035-A33E-A78793012509}" name="Tỷ lệ trong Phân khúc" dataDxfId="5"/>
-    <tableColumn id="5" xr3:uid="{2AC1F230-4A06-4948-AF77-F82B7A0737DF}" name="Tỷ lệ trên Toàn bộ (272 mã)" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{9F68D01C-71EB-49C8-B564-8B5B4D908E16}" name="Đặc trưng tóm tắt chuỗi dữ liệu (Heuristics)" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{6AA7C77C-10DD-412B-8689-CF83A58C625A}" name="Quyết định Lưu kho &amp; Điều phối thực tế (Đã tích hợp Trọng số Tết)" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{67327BFD-4040-4A35-8624-53C6C984AF0B}" name="Phân khúc"/>
+    <tableColumn id="2" xr3:uid="{962FA61A-800E-40D1-9418-84D31EC19ACB}" name="Mô hình Vô địch" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{11EE7554-B263-4FE5-AB95-DDF1B3E23B3E}" name="Số lượng mã" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{032CBEB0-EA6F-435B-A1A8-567114C9E53C}" name="Tỷ lệ trong Phân khúc" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{32BA8A28-B3E3-425D-8DEA-F16D06838EB7}" name="Tỷ lệ trên Toàn bộ (272 mã)" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{145E4EB4-6924-4ECB-8BA0-BEA308FD0B27}" name="Đặc trưng tóm tắt chuỗi dữ liệu (Heuristics)" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{4D29645C-7387-461C-8DD8-4830E9CD4D4E}" name="Quyết định Lưu kho &amp; Điều phối thực tế (Đã tích hợp Hậu xử lý)" dataDxfId="2"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -579,17 +544,15 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultColWidth="0" defaultRowHeight="15.75" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" zeroHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="35.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16.5703125" customWidth="1"/>
     <col min="3" max="3" width="14.140625" customWidth="1"/>
     <col min="4" max="4" width="21.28515625" customWidth="1"/>
     <col min="5" max="5" width="25.85546875" customWidth="1"/>
-    <col min="6" max="6" width="106.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="142.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="11" width="12.5703125" customWidth="1"/>
-    <col min="12" max="16384" width="12.5703125" hidden="1"/>
+    <col min="6" max="6" width="74.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="155.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -623,162 +586,162 @@
         <v>8</v>
       </c>
       <c r="C2" s="1">
-        <v>39</v>
-      </c>
-      <c r="D2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="2">
+        <v>0.375</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0.13200000000000001</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="1">
+        <v>25</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0.26</v>
+      </c>
+      <c r="E3" s="2">
+        <v>9.1999999999999998E-2</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>13</v>
-      </c>
-      <c r="C3" s="1">
-        <v>23</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B4" s="1" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="C4" s="1">
-        <v>18</v>
-      </c>
-      <c r="D4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>20</v>
+      <c r="D4" s="2">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="E4" s="2">
+        <v>7.0000000000000007E-2</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B5" s="1" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="C5" s="1">
         <v>16</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>25</v>
+      <c r="D5" s="2">
+        <v>0.16700000000000001</v>
+      </c>
+      <c r="E5" s="2">
+        <v>5.8999999999999997E-2</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C6" s="1">
         <v>97</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>31</v>
+      <c r="D6" s="2">
+        <v>0.55100000000000005</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0.35699999999999998</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>33</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B7" s="1" t="s">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C7" s="1">
         <v>38</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>36</v>
+      <c r="D7" s="2">
+        <v>0.216</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0.14000000000000001</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="C8" s="1">
         <v>25</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>41</v>
+      <c r="D8" s="2">
+        <v>0.14199999999999999</v>
+      </c>
+      <c r="E8" s="2">
+        <v>9.1999999999999998E-2</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B9" s="1" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="C9" s="1">
         <v>16</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>25</v>
+      <c r="D9" s="2">
+        <v>9.0999999999999998E-2</v>
+      </c>
+      <c r="E9" s="2">
+        <v>5.8999999999999997E-2</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
